--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,7 +265,7 @@
     <t>The parameters that may be used are defined by the OperationDefinition resource.</t>
   </si>
   <si>
-    <t xml:space="preserve">access-unalign-condition-required:When the unalignment reason is 'no-longer-clinically-eligible', at least one condition parameter must be provided to document the disqualifying diagnosis {parameter.where(name = 'reason').value.ofType(CodeableConcept).coding.where(system = 'https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentReasonCS' and code = 'no-longer-clinically-eligible').exists() implies parameter.where(name = 'conditions').exists()}
+    <t xml:space="preserve">access-unalign-condition-required:When the unalignment reason is 'no-longer-clinically-eligible', at least one condition parameter must be provided to document the disqualifying diagnosis {parameter.where(name = 'reason').value.ofType(CodeableConcept).coding.where(system = 'https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentReasonCS' and code = 'no-longer-clinically-eligible').exists() implies parameter.where(name = 'condition').exists()}
 </t>
   </si>
   <si>
@@ -651,7 +651,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -660,31 +660,31 @@
     <t>Parameters.parameter:track.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions</t>
-  </si>
-  <si>
-    <t>conditions</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:conditions.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-condition|0.7.0}
+    <t>Parameters.parameter:condition</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:condition.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-clinical-exclusion-condition|0.9.0}
 </t>
   </si>
   <si>
@@ -697,7 +697,7 @@
     <t>Observation[classCode=OBS, moodCode=EVN, code=ASSERTION, value&lt;Diagnosis]</t>
   </si>
   <si>
-    <t>Parameters.parameter:conditions.part</t>
+    <t>Parameters.parameter:condition.part</t>
   </si>
   <si>
     <t>Parameters.parameter:reason</t>
@@ -721,7 +721,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentReasonVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentReasonVS|0.9.0</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>
@@ -3252,7 +3252,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4108,7 +4108,7 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4858,7 +4858,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -5818,7 +5818,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6568,7 +6568,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7528,7 +7528,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-unalign-in</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-unalign-in</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,7 +265,7 @@
     <t>The parameters that may be used are defined by the OperationDefinition resource.</t>
   </si>
   <si>
-    <t xml:space="preserve">access-unalign-condition-required:When the unalignment reason is 'no-longer-clinically-eligible', at least one condition parameter must be provided to document the disqualifying diagnosis {parameter.where(name = 'reason').value.ofType(CodeableConcept).coding.where(system = 'https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentReasonCS' and code = 'no-longer-clinically-eligible').exists() implies parameter.where(name = 'condition').exists()}
+    <t xml:space="preserve">access-unalign-condition-required:When the unalignment reason is 'no-longer-clinically-eligible', at least one condition parameter must be provided to document the disqualifying diagnosis {parameter.where(name = 'reason').value.ofType(CodeableConcept).coding.where(system = 'https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSUnalignmentReasonCS' and code = 'no-longer-clinically-eligible').exists() implies parameter.where(name = 'condition').exists()}
 </t>
   </si>
   <si>
@@ -651,7 +651,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSTrackVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -684,7 +684,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://globalalliantinc.com/access/StructureDefinition/access-clinical-exclusion-condition|0.9.0}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.1}
 </t>
   </si>
   <si>
@@ -721,7 +721,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentReasonVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.1</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>
@@ -1072,7 +1072,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.0859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -355,9 +355,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -543,7 +540,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCESS#### where #### represents exactly 4 digits (e.g., ACCESS0001, ACCESS1234) {value.matches('^ACCESS\\d{4}$')}</t>
+access-participant-id-pattern:ACCESS Participant ID must follow the pattern ACCES##### where ##### represents exactly 5 digits (e.g., ACCES00001, ACCES12345) {value.matches('^ACCES\\d{5}$')}</t>
   </si>
   <si>
     <t>Parameters.parameter:participantID.resource</t>
@@ -651,7 +648,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -684,7 +681,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.1}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.6}
 </t>
   </si>
   <si>
@@ -721,7 +718,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.6</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>
@@ -1697,29 +1694,27 @@
       <c r="X6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1742,10 +1737,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1753,7 +1748,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>77</v>
@@ -1768,13 +1763,13 @@
         <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1813,17 +1808,17 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1835,7 +1830,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1872,13 +1867,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1929,7 +1924,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1952,14 +1947,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1978,16 +1973,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2037,7 +2032,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2049,7 +2044,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2060,14 +2055,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2086,19 +2081,19 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2147,7 +2142,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2159,21 +2154,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2196,13 +2191,13 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2253,7 +2248,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>85</v>
@@ -2276,10 +2271,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2302,13 +2297,13 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2359,7 +2354,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2368,7 +2363,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2382,10 +2377,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2408,16 +2403,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2467,7 +2462,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2476,7 +2471,7 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2490,10 +2485,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2519,13 +2514,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2575,7 +2570,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2598,13 +2593,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2626,13 +2621,13 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2683,7 +2678,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2695,7 +2690,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2706,10 +2701,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2732,13 +2727,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2789,7 +2784,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2812,14 +2807,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2838,16 +2833,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2897,7 +2892,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2909,7 +2904,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2920,10 +2915,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2946,13 +2941,13 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3003,7 +2998,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3015,7 +3010,7 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
@@ -3026,10 +3021,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3052,13 +3047,13 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3067,7 +3062,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3109,7 +3104,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3132,10 +3127,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3158,13 +3153,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3215,7 +3210,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3224,10 +3219,10 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3238,10 +3233,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3264,16 +3259,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3323,7 +3318,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3332,7 +3327,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3346,10 +3341,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3375,13 +3370,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3431,7 +3426,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3454,13 +3449,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3482,13 +3477,13 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3539,7 +3534,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3551,7 +3546,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3562,10 +3557,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3588,13 +3583,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3645,7 +3640,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3668,14 +3663,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3694,16 +3689,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3753,7 +3748,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3765,7 +3760,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3776,10 +3771,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3802,13 +3797,13 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3859,7 +3854,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3871,7 +3866,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3882,10 +3877,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3908,13 +3903,13 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3923,7 +3918,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3965,7 +3960,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -3988,10 +3983,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4014,13 +4009,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4071,7 +4066,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4080,7 +4075,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>97</v>
@@ -4094,10 +4089,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4120,16 +4115,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4179,7 +4174,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4188,7 +4183,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4202,10 +4197,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4231,13 +4226,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4287,7 +4282,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4310,13 +4305,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4338,13 +4333,13 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4395,7 +4390,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4407,7 +4402,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4418,10 +4413,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4444,13 +4439,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4501,7 +4496,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4524,14 +4519,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4550,16 +4545,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4609,7 +4604,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4621,7 +4616,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4632,10 +4627,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4658,13 +4653,13 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4715,7 +4710,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4727,7 +4722,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4738,10 +4733,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4764,13 +4759,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4779,7 +4774,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4821,7 +4816,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -4844,10 +4839,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4870,13 +4865,13 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4927,7 +4922,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4936,7 +4931,7 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>97</v>
@@ -4950,14 +4945,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -4976,16 +4971,16 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5035,7 +5030,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5053,15 +5048,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5087,13 +5082,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5143,7 +5138,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5166,13 +5161,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5194,13 +5189,13 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5251,7 +5246,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5263,7 +5258,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5274,10 +5269,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5300,13 +5295,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5357,7 +5352,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5380,14 +5375,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5406,16 +5401,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5465,7 +5460,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5477,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5488,10 +5483,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5514,13 +5509,13 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5571,7 +5566,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5583,7 +5578,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5594,10 +5589,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5620,13 +5615,13 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5635,7 +5630,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5677,7 +5672,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -5700,10 +5695,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5726,13 +5721,13 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5759,11 +5754,11 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5781,7 +5776,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5790,7 +5785,7 @@
         <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>97</v>
@@ -5804,10 +5799,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5830,16 +5825,16 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5889,7 +5884,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5898,7 +5893,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5912,10 +5907,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5941,13 +5936,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5997,7 +5992,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6020,13 +6015,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6048,13 +6043,13 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6105,7 +6100,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6117,7 +6112,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6128,10 +6123,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6154,13 +6149,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6211,7 +6206,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6234,14 +6229,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6260,16 +6255,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6319,7 +6314,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6331,7 +6326,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6342,10 +6337,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6368,13 +6363,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6425,7 +6420,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6437,7 +6432,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6448,10 +6443,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6474,13 +6469,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6489,7 +6484,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6531,7 +6526,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>85</v>
@@ -6554,10 +6549,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6580,13 +6575,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6637,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6646,7 +6641,7 @@
         <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>97</v>
@@ -6660,10 +6655,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6686,16 +6681,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6745,7 +6740,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6760,18 +6755,18 @@
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6797,13 +6792,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6853,7 +6848,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6876,13 +6871,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>75</v>
@@ -6904,13 +6899,13 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6961,7 +6956,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -6973,7 +6968,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -6984,10 +6979,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7010,13 +7005,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7067,7 +7062,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7090,14 +7085,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7116,16 +7111,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7175,7 +7170,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7187,7 +7182,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7198,10 +7193,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7224,13 +7219,13 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7281,7 +7276,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7293,7 +7288,7 @@
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -7304,10 +7299,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7330,13 +7325,13 @@
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7345,7 +7340,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7387,7 +7382,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>85</v>
@@ -7410,10 +7405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7436,13 +7431,13 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7469,11 +7464,11 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7491,7 +7486,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7500,7 +7495,7 @@
         <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>97</v>
@@ -7514,10 +7509,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7540,16 +7535,16 @@
         <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7599,7 +7594,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7608,7 +7603,7 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>75</v>
@@ -7622,10 +7617,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7651,13 +7646,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7707,7 +7702,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -648,7 +648,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -681,7 +681,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.6}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.8}
 </t>
   </si>
   <si>
@@ -718,7 +718,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="272">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -317,13 +317,187 @@
 </t>
   </si>
   <si>
-    <t>Parameters.implicitRules</t>
+    <t>Parameters.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Parameters.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Parameters.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Parameters.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Parameters.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Parameters.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Parameters.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Parameters.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -391,44 +565,7 @@
     <t>Parameters.parameter.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Parameters.parameter.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Parameters.parameter.modifierExtension</t>
@@ -648,7 +785,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -681,7 +818,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.8}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.11}
 </t>
   </si>
   <si>
@@ -718,7 +855,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>
@@ -1041,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL62"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.69921875" customWidth="true" bestFit="true"/>
@@ -1068,11 +1205,11 @@
     <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.66796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.66796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -1428,7 +1565,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>85</v>
@@ -1543,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>99</v>
@@ -1557,9 +1694,7 @@
       <c r="M5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>75</v>
@@ -1608,7 +1743,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -1620,32 +1755,32 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -1692,55 +1827,57 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1748,13 +1885,13 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>75</v>
@@ -1763,7 +1900,7 @@
         <v>86</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>115</v>
@@ -1771,7 +1908,9 @@
       <c r="M7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>75</v>
@@ -1808,29 +1947,31 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AC7" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AF7" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1841,10 +1982,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1864,18 +2005,20 @@
         <v>75</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>75</v>
@@ -1936,13 +2079,13 @@
         <v>75</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" hidden="true">
@@ -1954,14 +2097,14 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>75</v>
@@ -1970,19 +2113,19 @@
         <v>75</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2032,41 +2175,41 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -2075,26 +2218,24 @@
         <v>75</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>75</v>
       </c>
@@ -2142,7 +2283,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2154,21 +2295,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2176,10 +2317,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2191,15 +2332,17 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2224,13 +2367,13 @@
         <v>75</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>75</v>
@@ -2248,13 +2391,13 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>75</v>
@@ -2271,10 +2414,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2285,7 +2428,7 @@
         <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>75</v>
@@ -2297,15 +2440,17 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>75</v>
@@ -2330,13 +2475,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2354,16 +2499,16 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2377,10 +2522,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2397,22 +2542,22 @@
         <v>75</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2462,7 +2607,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2471,10 +2616,10 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>75</v>
@@ -2485,10 +2630,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2499,7 +2644,7 @@
         <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>75</v>
@@ -2508,19 +2653,19 @@
         <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2546,13 +2691,11 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -2570,13 +2713,13 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>75</v>
@@ -2591,25 +2734,23 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>86</v>
@@ -2621,13 +2762,13 @@
         <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2666,19 +2807,17 @@
         <v>75</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2690,7 +2829,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2701,10 +2840,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2727,13 +2866,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2784,7 +2923,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2807,14 +2946,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2833,16 +2972,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2892,7 +3031,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2904,7 +3043,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2915,21 +3054,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -2941,16 +3080,20 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -2998,7 +3141,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3010,21 +3153,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3038,7 +3181,7 @@
         <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -3047,13 +3190,13 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3062,7 +3205,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -3104,7 +3247,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3125,12 +3268,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3138,13 +3281,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>75</v>
@@ -3153,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3210,7 +3353,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3219,10 +3362,10 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>75</v>
@@ -3233,10 +3376,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3247,7 +3390,7 @@
         <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -3259,16 +3402,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3318,7 +3461,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3327,7 +3470,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3341,10 +3484,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3367,16 +3510,16 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3426,7 +3569,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3449,13 +3592,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3477,13 +3620,13 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3534,7 +3677,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3546,7 +3689,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3557,10 +3700,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3583,13 +3726,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3640,7 +3783,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3663,14 +3806,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3689,16 +3832,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3748,7 +3891,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3760,7 +3903,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3771,10 +3914,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3797,13 +3940,13 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3854,7 +3997,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3866,7 +4009,7 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
@@ -3877,10 +4020,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3903,13 +4046,13 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3918,7 +4061,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3960,7 +4103,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>85</v>
@@ -3983,10 +4126,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4009,13 +4152,13 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4066,7 +4209,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4075,10 +4218,10 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>75</v>
@@ -4089,10 +4232,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4115,16 +4258,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>151</v>
+        <v>195</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4174,7 +4317,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4183,7 +4326,7 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4197,10 +4340,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4226,13 +4369,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4282,7 +4425,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4305,13 +4448,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>75</v>
@@ -4333,13 +4476,13 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4390,7 +4533,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4402,7 +4545,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4413,10 +4556,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4439,13 +4582,13 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4496,7 +4639,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4519,14 +4662,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4545,16 +4688,16 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4604,7 +4747,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4616,7 +4759,7 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -4627,10 +4770,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4653,13 +4796,13 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4710,7 +4853,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4722,7 +4865,7 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
@@ -4733,10 +4876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4759,13 +4902,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4774,7 +4917,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>75</v>
@@ -4816,7 +4959,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>85</v>
@@ -4837,12 +4980,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4850,13 +4993,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -4865,13 +5008,13 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4922,7 +5065,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4931,7 +5074,7 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>97</v>
@@ -4943,44 +5086,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5030,7 +5173,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5039,7 +5182,7 @@
         <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5048,15 +5191,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>191</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5082,13 +5225,13 @@
         <v>78</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5138,7 +5281,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5161,13 +5304,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5189,13 +5332,13 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5246,7 +5389,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5258,7 +5401,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5269,10 +5412,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5295,13 +5438,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5352,7 +5495,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5375,14 +5518,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5401,16 +5544,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5460,7 +5603,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5472,7 +5615,7 @@
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
@@ -5483,10 +5626,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5509,13 +5652,13 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5566,7 +5709,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5578,7 +5721,7 @@
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
@@ -5589,10 +5732,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5615,13 +5758,13 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5630,7 +5773,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5672,7 +5815,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -5693,12 +5836,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5706,13 +5849,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
@@ -5721,13 +5864,13 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5754,11 +5897,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -5776,7 +5921,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5785,7 +5930,7 @@
         <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>97</v>
@@ -5797,44 +5942,44 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>149</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5884,7 +6029,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5893,7 +6038,7 @@
         <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -5902,15 +6047,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5936,13 +6081,13 @@
         <v>78</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5992,7 +6137,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6015,23 +6160,23 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>86</v>
@@ -6043,13 +6188,13 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6100,7 +6245,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6112,7 +6257,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6123,10 +6268,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6149,13 +6294,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6206,7 +6351,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6229,14 +6374,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6255,16 +6400,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6314,7 +6459,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6326,7 +6471,7 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
@@ -6337,10 +6482,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6363,13 +6508,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6420,7 +6565,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6432,7 +6577,7 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6443,10 +6588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6469,13 +6614,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6484,7 +6629,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>75</v>
@@ -6526,7 +6671,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>85</v>
@@ -6547,12 +6692,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6560,13 +6705,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
@@ -6575,13 +6720,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>144</v>
+        <v>244</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6608,13 +6753,11 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6632,7 +6775,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6641,7 +6784,7 @@
         <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>97</v>
@@ -6653,12 +6796,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6666,31 +6809,31 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6740,7 +6883,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6749,24 +6892,24 @@
         <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6792,13 +6935,13 @@
         <v>78</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6848,7 +6991,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6871,23 +7014,23 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>86</v>
@@ -6899,13 +7042,13 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6956,7 +7099,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -6968,7 +7111,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -6979,10 +7122,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7005,13 +7148,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7062,7 +7205,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7085,14 +7228,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7111,16 +7254,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7170,7 +7313,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7182,7 +7325,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7193,10 +7336,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7219,13 +7362,13 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>163</v>
+        <v>207</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7276,7 +7419,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7288,7 +7431,7 @@
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
@@ -7299,10 +7442,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7325,13 +7468,13 @@
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7340,7 +7483,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7382,7 +7525,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>85</v>
@@ -7403,12 +7546,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7416,13 +7559,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -7431,13 +7574,13 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7464,11 +7607,13 @@
         <v>75</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -7486,7 +7631,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -7495,7 +7640,7 @@
         <v>85</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>97</v>
@@ -7507,12 +7652,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7520,31 +7665,31 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7594,7 +7739,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -7603,24 +7748,24 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>75</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7646,13 +7791,13 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>155</v>
+        <v>199</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7702,7 +7847,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -7723,8 +7868,862 @@
         <v>75</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL62">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7734,7 +8733,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-unalign-in.xlsx
+++ b/StructureDefinition-access-unalign-in.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -785,7 +785,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSTrackVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:track.resource</t>
@@ -818,7 +818,7 @@
     <t>Parameters.parameter:condition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.11}
+    <t xml:space="preserve">Condition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-clinical-exclusion-condition|0.9.12}
 </t>
   </si>
   <si>
@@ -855,7 +855,7 @@
     <t>Parameters.parameter:reason.value[x]</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentReasonVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:reason.resource</t>
